--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-01.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-01.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,12 +595,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -759,12 +759,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -838,12 +838,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0x4</t>
+          <t>0-4</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -917,12 +917,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2x4</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -996,12 +996,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0x5</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-01.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-01.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,12 +595,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -759,12 +759,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -838,12 +838,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0-4</t>
+          <t>0x4</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -917,12 +917,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>2x4</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -996,12 +996,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>0x5</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-01.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-01.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -674,19 +674,19 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -1636,19 +1636,19 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>5x0</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S15" t="n">
